--- a/arquivos/custos_nfv.xlsx
+++ b/arquivos/custos_nfv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao nfv automatico\NEW_NFV\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A58E28B-F3B0-4CCD-9996-83E0D57983D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE80F6FB-EAEE-48A6-8AAF-838AF0E1E650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="3">
-        <v>10559</v>
+        <v>1074</v>
       </c>
       <c r="C13" s="3">
-        <v>10559</v>
+        <v>1074</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
       </c>
       <c r="E13" s="3">
-        <v>1328</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
